--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-documentreference.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-documentreference.xlsx
@@ -274,14 +274,14 @@
     <t>ドキュメントへの参照 / A reference to a document</t>
   </si>
   <si>
-    <t>あらゆる目的のためのあらゆる種類の文書への参照。ドキュメントを検出および管理できるように、ドキュメントに関するメタデータを提供します。ドキュメントの範囲は、MIMEタイプを備えたセラル化オブジェクトであるため、正式な患者中心のドキュメント（CDA）、Cliical Notes、スキャンされた論文、およびポリシーテキストなどの非患者固有の文書が含まれています。 / A reference to a document of any kind for any purpose. Provides metadata about the document so that the document can be discovered and managed. The scope of a document is any seralized object with a mime-type, so includes formal patient centric documents (CDA), cliical notes, scanned paper, and non-patient specific documents like policy text.</t>
+    <t>あらゆる目的のためのあらゆる種類の文書への参照。ドキュメントを検出および管理できるように、ドキュメントに関するMetadataを提供します。ドキュメントの範囲は、MIMEタイプを備えたセラル化オブジェクトであるため、正式な患者中心のドキュメント（CDA）、Cliical Notes、スキャンされた論文、およびポリシーテキストなどの非患者固有の文書が含まれています。 / A reference to a document of any kind for any purpose. Provides metadata about the document so that the document can be discovered and managed. The scope of a document is any seralized object with a mime-type, so includes formal patient centric documents (CDA), cliical notes, scanned paper, and non-patient specific documents like policy text.</t>
   </si>
   <si>
     <t>通常、これはFHIRによって定義されたもの以外のドキュメントに使用されます。 / Usually, this is used for documents other than those defined by FHIR.</t>
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -328,16 +328,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -374,7 +374,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -394,16 +394,16 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>DocumentReference.meta.versionId</t>
   </si>
   <si>
-    <t>バージョン固有の識別子</t>
-  </si>
-  <si>
-    <t>URLのバージョン部分に表示されるバージョン固有の識別子。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
+    <t>バージョン固有のidentifier (Baajon koyū no shikibetsu-shi)</t>
+  </si>
+  <si>
+    <t>URLのバージョン部分に表示されるバージョン固有のidentifier。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
   </si>
   <si>
     <t>サーバーがこの値を割り当て、クライアントが指定した値を無視する。ただし、サーバーが更新/削除時にバージョンの整合性を強制する場合を除く。</t>
@@ -423,7 +423,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースのバージョンが最後に変更されたとき」</t>
+    <t>リソースのバージョンが最後に変更されたとき</t>
   </si>
   <si>
     <t>リソースが最後に変更されたとき - 例えば、バージョンが変更されたとき。</t>
@@ -448,8 +448,8 @@
     <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。</t>
   </si>
   <si>
-    <t>「プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
-この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。」</t>
+    <t>プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
+この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。</t>
   </si>
   <si>
     <t>Meta.source</t>
@@ -517,7 +517,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>「様々なタグを表すコードで、一般的にはワークフローに関連しています。</t>
+    <t>様々なタグを表すコードで、一般的にはワークフローに関連しています。例：「ジョーンズ博士によるレビューが必要です」。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/common-tags</t>
@@ -636,7 +636,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -664,10 +664,10 @@
 </t>
   </si>
   <si>
-    <t>マスターバージョン固有の識別子 / Master Version Specific Identifier</t>
-  </si>
-  <si>
-    <t>ドキュメントのソースによって割り当てられたドキュメント識別子。この識別子は、このバージョンのドキュメントに固有です。この一意の識別子は、このバージョンのドキュメントを識別するために他の場所で使用できます。 / Document identifier as assigned by the source of the document. This identifier is specific to this version of the document. This unique identifier may be used elsewhere to identify this version of the document.</t>
+    <t>マスターバージョン固有のidentifier / Master Version Specific Identifier</t>
+  </si>
+  <si>
+    <t>ドキュメントのソースによって割り当てられたドキュメントidentifier。このidentifierは、このバージョンのドキュメントに固有です。この一意のidentifierは、このバージョンのドキュメントを識別するために他の場所で使用できます。 / Document identifier as assigned by the source of the document. This identifier is specific to this version of the document. This unique identifier may be used elsewhere to identify this version of the document.</t>
   </si>
   <si>
     <t>CDAドキュメントID拡張機能とルート。 / CDA Document Id extension and root.</t>
@@ -700,10 +700,10 @@
     <t>DocumentReference.identifier</t>
   </si>
   <si>
-    <t>ドキュメントの他の識別子 / Other identifiers for the document</t>
-  </si>
-  <si>
-    <t>バージョンの独立識別子を含む、ドキュメントに関連付けられた他の識別子。 / Other identifiers associated with the document, including version independent identifiers.</t>
+    <t>ドキュメントの他のidentifier / Other identifiers for the document</t>
+  </si>
+  <si>
+    <t>バージョンの独立identifierを含む、ドキュメントに関連付けられた他のidentifier。 / Other identifiers associated with the document, including version independent identifiers.</t>
   </si>
   <si>
     <t>.id / .setId</t>
@@ -793,7 +793,7 @@
     <t>参照されている特定の種類のドキュメントを指定します（例：履歴と物理的、排出概要、進行状況ノート）。これは通常、文書を参照する目的に相当します。 / Specifies the particular kind of document referenced  (e.g. History and Physical, Discharge Summary, Progress Note). This usually equates to the purpose of making the document referenced.</t>
   </si>
   <si>
-    <t>彼が正確なタイプのドキュメントを説明するドキュメントを説明する重要なメタデータ要素。ドキュメントのリストを表示する際に、人間がドキュメントが興味深いかどうかを評価するのに役立ちます。 / Key metadata element describing the document that describes he exact type of document. Helps humans to assess whether the document is of interest when viewing a list of documents.</t>
+    <t>彼が正確なタイプのドキュメントを説明するドキュメントを説明する重要なMetadata要素。ドキュメントのリストを表示する際に、人間がドキュメントが興味深いかどうかを評価するのに役立ちます。 / Key metadata element describing the document that describes he exact type of document. Helps humans to assess whether the document is of interest when viewing a list of documents.</t>
   </si>
   <si>
     <t>正確なタイプの臨床文書。 / Precise type of clinical document.</t>
@@ -837,7 +837,7 @@
     <t>参照されるドキュメントのタイプの分類 - インデックス作成と検索に役立ちます。これは、documentreference.typeで指定されたコードによって暗示または導出される場合があります。 / A categorization for the type of document referenced - helps for indexing and searching. This may be implied by or derived from the code specified in the DocumentReference.type.</t>
   </si>
   <si>
-    <t>ドキュメントのカテゴリまたは分類を説明する重要なメタデータ要素。これは、使用方法に基づいて同様のドキュメントをグループ化するより広範な視点です。これは、検索に使用される主要なキーです。 / Key metadata element describing the the category or classification of the document. This is a broader perspective that groups similar documents based on how they would be used. This is a primary key used in searching.</t>
+    <t>ドキュメントのカテゴリまたは分類を説明する重要なMetadata要素。これは、使用方法に基づいて同様のドキュメントをグループ化するより広範な視点です。これは、検索に使用される主要なキーです。 / Key metadata element describing the the category or classification of the document. This is a broader perspective that groups similar documents based on how they would be used. This is a primary key used in searching.</t>
   </si>
   <si>
     <t>マクロレベルでの高レベルの臨床文書。 / High-level kind of a clinical document at a macro level.</t>
@@ -1210,7 +1210,7 @@
     <t>ドキュメントにアクセスする場所 / Where to access the document</t>
   </si>
   <si>
-    <t>ドキュメントのドキュメントまたはURLと、コンテンツに整合性があることを証明する重要なメタデータがあります。 / The document or URL of the document along with critical metadata to prove content has integrity.</t>
+    <t>ドキュメントのドキュメントまたはURLと、コンテンツに整合性があることを証明する重要なMetadataがあります。 / The document or URL of the document along with critical metadata to prove content has integrity.</t>
   </si>
   <si>
     <t>Composition.language, 
@@ -1233,7 +1233,7 @@
     <t>ドキュメントのフォーマット/コンテンツルール / Format/content rules for the document</t>
   </si>
   <si>
-    <t>ドキュメントがエンコード、構造、およびテンプレートの識別子は、ドキュメントがMIMETYPEに示されているベース形式を超えて適合することです。 / An identifier of the document encoding, structure, and template that the document conforms to beyond the base format indicated in the mimeType.</t>
+    <t>ドキュメントがエンコード、構造、およびテンプレートのidentifierは、ドキュメントがMIMETYPEに示されているベース形式を超えて適合することです。 / An identifier of the document encoding, structure, and template that the document conforms to beyond the base format indicated in the mimeType.</t>
   </si>
   <si>
     <t>iheは主にフォーマットタイプのurnsを発行しますが、すべてのドキュメントがURIで識別できるわけではないことに注意してください。 / Note that while IHE mostly issues URNs for format types, not all documents can be identified by a URI.</t>
@@ -1309,10 +1309,10 @@
     <t>主な臨床行為が文書化されています / Main clinical acts documented</t>
   </si>
   <si>
-    <t>このコードのリストは、文書化されている大腸内視鏡検査や虫垂切除術などの主要な臨床行為を表しています。場合によっては、このイベントは、文書化されている手順が必然的に「歴史と物理的」行為である「履歴と物理的報告」など、タイプコードに固有のものです。 / This list of codes represents the main clinical acts, such as a colonoscopy or an appendectomy, being documented. In some cases, the event is inherent in the type Code, such as a "History and Physical Report" in which the procedure being documented is necessarily a "History and Physical" act.</t>
-  </si>
-  <si>
-    <t>イベントは、単に「手順報告書」であり、手順は「大腸鏡検査」であるなど、タイプに固有の行為をさらに専門化することができます。1つ以上のイベントコードが含まれている場合、クラスまたはタイプの要素に固有の値と矛盾してはなりません。そのような競合が曖昧な状況を生み出すためです。 / An event can further specialize the act inherent in the type, such as  where it is simply "Procedure Report" and the procedure was a "colonoscopy". If one or more event codes are included, they shall not conflict with the values inherent in the class or type elements as such a conflict would create an ambiguous situation.</t>
+    <t>このコードのリストは、文書化されている大腸内視鏡検査や虫垂切除術などの主要な臨床行為を表しています。場合によっては、このイベントは、文書化されているプロシジャー（処置等）が必然的に「歴史と物理的」行為である「履歴と物理的報告」など、タイプコードに固有のものです。 / This list of codes represents the main clinical acts, such as a colonoscopy or an appendectomy, being documented. In some cases, the event is inherent in the type Code, such as a "History and Physical Report" in which the procedure being documented is necessarily a "History and Physical" act.</t>
+  </si>
+  <si>
+    <t>イベントは、単に「プロシジャー（処置等）報告書」であり、プロシジャー（処置等）は「大腸鏡検査」であるなど、タイプに固有の行為をさらに専門化することができます。1つ以上のイベントコードが含まれている場合、クラスまたはタイプの要素に固有の値と矛盾してはなりません。そのような競合が曖昧な状況を生み出すためです。 / An event can further specialize the act inherent in the type, such as  where it is simply "Procedure Report" and the procedure was a "colonoscopy". If one or more event codes are included, they shall not conflict with the values inherent in the class or type elements as such a conflict would create an ambiguous situation.</t>
   </si>
   <si>
     <t>このコードのリストは、文書化されている主要な臨床行為を表しています。 / This list of codes represents the main clinical acts being documented.</t>
@@ -1398,7 +1398,7 @@
     <t>この要素は、専門診療のクラスのための粗い分類システムに基づいている必要があります。LOINCの主題ドメインによって記述されているような練習設定に分類システムの使用を推奨します。 / This element should be based on a coarse classification system for the class of specialty practice. Recommend the use of the classification system for Practice Setting, such as that described by the Subject Matter Domain in LOINC.</t>
   </si>
   <si>
-    <t>これは、プロバイダーがしばしば迅速にソートおよび/または除外して特定のコンテンツを見つけるために依存する重要なメタデータです。 / This is an important piece of metadata that providers often rely upon to quickly sort and/or filter out to find specific content.</t>
+    <t>これは、プロバイダーがしばしば迅速にソートおよび/または除外して特定のコンテンツを見つけるために依存する重要なMetadataです。 / This is an important piece of metadata that providers often rely upon to quickly sort and/or filter out to find specific content.</t>
   </si>
   <si>
     <t>コンテンツが作成された場所に関する追加の詳細（臨床専門分野など）。 / Additional details about where the content was created (e.g. clinical specialty).</t>
@@ -1433,13 +1433,13 @@
 </t>
   </si>
   <si>
-    <t>関連する識別子またはリソース / Related identifiers or resources</t>
-  </si>
-  <si>
-    <t>ドキュメントレファレンスに関連する関連識別子またはリソース。 / Related identifiers or resources associated with the DocumentReference.</t>
-  </si>
-  <si>
-    <t>ドキュメントレファレンスまたは参照されたドキュメントを作成した識別子またはリソースが作成される場合があります。 / May be identifiers or resources that caused the DocumentReference or referenced Document to be created.</t>
+    <t>関連するidentifierまたはリソース / Related identifiers or resources</t>
+  </si>
+  <si>
+    <t>ドキュメントレファレンスに関連する関連identifierまたはリソース。 / Related identifiers or resources associated with the DocumentReference.</t>
+  </si>
+  <si>
+    <t>ドキュメントレファレンスまたは参照されたドキュメントを作成したidentifierまたはリソースが作成される場合があります。 / May be identifiers or resources that caused the DocumentReference or referenced Document to be created.</t>
   </si>
   <si>
     <t>Composition.event.detail</t>
